--- a/originales/respuestas/2025/01. Calificadas/bucle p16/Alcaldía Local De Tunjuelito.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p16/Alcaldía Local De Tunjuelito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/Esteban 2/bucle p16/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12E5A777-2E17-4B59-A9D2-E72A87C0B0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024B5FFE-72E7-9C4F-A054-3287ACD56FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1B121F2D-5148-48E9-97E2-8293CA9AC78C}"/>
+    <workbookView xWindow="-120" yWindow="740" windowWidth="19420" windowHeight="10300" xr2:uid="{1B121F2D-5148-48E9-97E2-8293CA9AC78C}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -127,7 +127,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,11 +139,21 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -235,10 +245,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -252,8 +263,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -568,9 +583,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6B2F3EB-131B-4FBE-8FAA-71C9BD3E7693}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="42" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -626,7 +641,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="337.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="332" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>18</v>
       </c>
@@ -643,42 +658,42 @@
       <c r="F2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="M2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>27</v>
       </c>
       <c r="O2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P2" s="4" t="s">
         <v>28</v>
       </c>
       <c r="Q2" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -726,7 +741,7 @@
       </c>
       <c r="R3" s="4"/>
     </row>
-    <row r="4" spans="1:18" ht="87.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="98" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
@@ -770,7 +785,7 @@
       </c>
       <c r="R4" s="4"/>
     </row>
-    <row r="5" spans="1:18" ht="112.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="126" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
@@ -814,7 +829,7 @@
       </c>
       <c r="R5" s="4"/>
     </row>
-    <row r="6" spans="1:18" ht="87.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="98" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
@@ -857,6 +872,9 @@
       <c r="R6" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{7857C016-A959-4F48-A559-597ECEC4FFB0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/originales/respuestas/2025/01. Calificadas/bucle p16/Alcaldía Local De Tunjuelito.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p16/Alcaldía Local De Tunjuelito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/Esteban 2/bucle p16/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/IIP - Esteban/bucle p16/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024B5FFE-72E7-9C4F-A054-3287ACD56FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E66FEC8-6CF6-B246-83E5-B7CD5591A4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="740" windowWidth="19420" windowHeight="10300" xr2:uid="{1B121F2D-5148-48E9-97E2-8293CA9AC78C}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{1B121F2D-5148-48E9-97E2-8293CA9AC78C}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Entidad</t>
   </si>
@@ -112,15 +112,6 @@
   </si>
   <si>
     <t>Relación de la taxonomía con la misionalidad de la entidad.</t>
-  </si>
-  <si>
-    <t>Eficiencia administrativa</t>
-  </si>
-  <si>
-    <t>Deficiencia administrativa para verificar y recopilar a través de un sistema ágil y oportuno las cuentas de cobro de los contratistas (persona natural). En el proceso de trámite de cuentas de cobro presentadas por los contratistas personas naturales, se identifico una problemática relacionada con los altos tiempos de respuesta en la gestión de pagos. Esta situación se debe principalmente al elevado volumen de devoluciones generadas durante el flujo de aprobación, ocasionadas por errores cometidos por los mismos contratistas que enviaron los formatos de la cuenta de cobro. Estos errores no solo retrasan el ciclo de aprobación, sino que también impactan negativamente en la eficiencia operativa del área responsable, generando insatisfacción tanto en los contratistas como en la entidad contratante.</t>
-  </si>
-  <si>
-    <t>Eficiencia administrativa, Servicio al ciudadano, Transparencia y rendición de cuentas</t>
   </si>
 </sst>
 </file>
@@ -582,7 +573,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6B2F3EB-131B-4FBE-8FAA-71C9BD3E7693}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:18" ht="42" x14ac:dyDescent="0.2">
@@ -692,184 +683,6 @@
         <v>1</v>
       </c>
       <c r="R2" s="4"/>
-    </row>
-    <row r="3" spans="1:18" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="4">
-        <v>5</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="4">
-        <v>5</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="4">
-        <v>5</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="4">
-        <v>5</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>5</v>
-      </c>
-      <c r="R3" s="4"/>
-    </row>
-    <row r="4" spans="1:18" ht="98" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="4">
-        <v>5</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="4">
-        <v>5</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="4">
-        <v>5</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="4">
-        <v>5</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>5</v>
-      </c>
-      <c r="R4" s="4"/>
-    </row>
-    <row r="5" spans="1:18" ht="126" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="4">
-        <v>5</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="4">
-        <v>5</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="4">
-        <v>5</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" s="4">
-        <v>5</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>5</v>
-      </c>
-      <c r="R5" s="4"/>
-    </row>
-    <row r="6" spans="1:18" ht="98" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="4">
-        <v>5</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="4">
-        <v>5</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" s="4">
-        <v>5</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="4">
-        <v>5</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>5</v>
-      </c>
-      <c r="R6" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
